--- a/main/ig/StructureDefinition-fr-lm-encounter.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-encounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-18T14:11:29+00:00</t>
+    <t>2026-05-21T09:18:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-encounter.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-encounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-21T09:18:21+00:00</t>
+    <t>2026-06-01T14:41:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-encounter.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-encounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-01T14:41:15+00:00</t>
+    <t>2026-06-01T15:18:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-encounter.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-encounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-01T15:18:33+00:00</t>
+    <t>2026-06-02T07:35:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-encounter.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-encounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-02T07:35:19+00:00</t>
+    <t>2026-06-04T15:31:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-encounter.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-encounter.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="724" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1251" uniqueCount="189">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-04T15:31:02+00:00</t>
+    <t>2026-06-16T14:27:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -293,6 +293,9 @@
   </si>
   <si>
     <t>fr-lm-encounter.header.author[x]</t>
+  </si>
+  <si>
+    <t>Responsable de la rencontre</t>
   </si>
   <si>
     <t>author[x] peut correspondre soit à un professionnel, soit à une organisation, soit à un système.</t>
@@ -448,22 +451,156 @@
     <t>fr-lm-entry.header.language</t>
   </si>
   <si>
-    <t>fr-lm-encounter.typeRencontre</t>
-  </si>
-  <si>
-    <t>Type de rencontre</t>
-  </si>
-  <si>
-    <t>fr-lm-encounter.dateRencontre</t>
-  </si>
-  <si>
-    <t>Date de la rencontre</t>
-  </si>
-  <si>
-    <t>fr-lm-encounter.confirmationRencontre</t>
-  </si>
-  <si>
-    <t>Confirmation attendue</t>
+    <t>fr-lm-encounter.participant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-participant
+</t>
+  </si>
+  <si>
+    <t>Personne impliquée dans la rencontre</t>
+  </si>
+  <si>
+    <t>fr-lm-encounter.period</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Period
+</t>
+  </si>
+  <si>
+    <t>Date de début et de fin de la rencontre.</t>
+  </si>
+  <si>
+    <t>fr-lm-encounter.priority</t>
+  </si>
+  <si>
+    <t>Priorité de la rencontre (ex : urgence, etc.).</t>
+  </si>
+  <si>
+    <t>fr-lm-encounter.type</t>
+  </si>
+  <si>
+    <t>Type de la rencontre (hospitalisation, soins à domicile, etc.).</t>
+  </si>
+  <si>
+    <t>fr-lm-encounter.serviceProvider</t>
+  </si>
+  <si>
+    <t>Organisation (établissement) responsable de cette rencontre</t>
+  </si>
+  <si>
+    <t>fr-lm-encounter.referringProfessional</t>
+  </si>
+  <si>
+    <t>Professionnel de santé référent</t>
+  </si>
+  <si>
+    <t>fr-lm-encounter.basedOn[x]</t>
+  </si>
+  <si>
+    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-care-plan
+https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-service-request</t>
+  </si>
+  <si>
+    <t>Référence à la demande ayant initié cette rencontre</t>
+  </si>
+  <si>
+    <t>fr-lm-encounter.reason[x]</t>
+  </si>
+  <si>
+    <t>CodeableConcept
+https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-conditionhttps://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-procedurehttps://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-observationstring</t>
+  </si>
+  <si>
+    <t>Motif(s) de l'admission, ex : problème, procédure ou constatation.</t>
+  </si>
+  <si>
+    <t>fr-lm-encounter.admission</t>
+  </si>
+  <si>
+    <t>Détails de l'admission</t>
+  </si>
+  <si>
+    <t>fr-lm-encounter.admission.admitter</t>
+  </si>
+  <si>
+    <t>Professionnel de santé ayant admis le patient</t>
+  </si>
+  <si>
+    <t>fr-lm-encounter.admission.admitSource</t>
+  </si>
+  <si>
+    <t>Source de l'admission (ex : référence d'un médecin, transfert).</t>
+  </si>
+  <si>
+    <t>fr-lm-encounter.dischargeDiagnosis[x]</t>
+  </si>
+  <si>
+    <t>CodeableConcept
+https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-condition</t>
+  </si>
+  <si>
+    <t>Les diagnostics au moment de la sortie.</t>
+  </si>
+  <si>
+    <t>fr-lm-encounter.dischargeDestination</t>
+  </si>
+  <si>
+    <t>Type et lieu de sortie</t>
+  </si>
+  <si>
+    <t>fr-lm-encounter.dischargeDestination.type</t>
+  </si>
+  <si>
+    <t>Type de sortie</t>
+  </si>
+  <si>
+    <t>fr-lm-encounter.dischargeDestination.location[x]</t>
+  </si>
+  <si>
+    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-organisation
+https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-location</t>
+  </si>
+  <si>
+    <t>Le lieu ou l'organisation</t>
+  </si>
+  <si>
+    <t>fr-lm-encounter.serviceLocation</t>
+  </si>
+  <si>
+    <t>Liste des lieux où le patient était présent pendant cette rencontre.</t>
+  </si>
+  <si>
+    <t>fr-lm-encounter.serviceLocation.period</t>
+  </si>
+  <si>
+    <t>Période pendant laquelle le patient était présent au lieu</t>
+  </si>
+  <si>
+    <t>fr-lm-encounter.serviceLocation.organisationPart[x]</t>
+  </si>
+  <si>
+    <t>Organisation ou partie d'une organisation (ex : département) où le patient était présent pendant la rencontre.</t>
+  </si>
+  <si>
+    <t>fr-lm-encounter.subEncounter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-encounter
+</t>
+  </si>
+  <si>
+    <t>référence aux rencontres considérées comme faisant partie de cette rencontre.</t>
+  </si>
+  <si>
+    <t>fr-lm-encounter.note</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string
+</t>
+  </si>
+  <si>
+    <t>Notes</t>
   </si>
 </sst>
 </file>
@@ -765,7 +902,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AJ22"/>
+  <dimension ref="A1:AJ39"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="49.5390625" customWidth="true" bestFit="true"/>
@@ -778,7 +915,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="73.875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="203.6484375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1349,7 +1486,7 @@
         <v>92</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="N6" s="2"/>
       <c r="O6" s="2"/>
@@ -1400,7 +1537,7 @@
         <v>73</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>74</v>
@@ -1417,10 +1554,10 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
@@ -1443,13 +1580,13 @@
         <v>73</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
@@ -1500,7 +1637,7 @@
         <v>73</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>74</v>
@@ -1517,10 +1654,10 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
@@ -1543,13 +1680,13 @@
         <v>73</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
@@ -1600,7 +1737,7 @@
         <v>73</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>74</v>
@@ -1617,10 +1754,10 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -1643,13 +1780,13 @@
         <v>73</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -1700,7 +1837,7 @@
         <v>73</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>74</v>
@@ -1717,10 +1854,10 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
@@ -1743,13 +1880,13 @@
         <v>73</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -1800,7 +1937,7 @@
         <v>73</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>74</v>
@@ -1817,10 +1954,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -1831,7 +1968,7 @@
         <v>74</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H11" t="s" s="2">
         <v>73</v>
@@ -1846,10 +1983,10 @@
         <v>80</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -1900,7 +2037,7 @@
         <v>73</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>74</v>
@@ -1917,10 +2054,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -1943,13 +2080,13 @@
         <v>73</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -2000,7 +2137,7 @@
         <v>73</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>74</v>
@@ -2017,10 +2154,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2043,13 +2180,13 @@
         <v>73</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
@@ -2100,7 +2237,7 @@
         <v>73</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>74</v>
@@ -2117,10 +2254,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2143,13 +2280,13 @@
         <v>73</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -2200,7 +2337,7 @@
         <v>73</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>74</v>
@@ -2217,10 +2354,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2243,13 +2380,13 @@
         <v>73</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -2300,7 +2437,7 @@
         <v>73</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>74</v>
@@ -2317,10 +2454,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2343,13 +2480,13 @@
         <v>73</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -2400,7 +2537,7 @@
         <v>73</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>74</v>
@@ -2417,10 +2554,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -2443,13 +2580,13 @@
         <v>73</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -2500,7 +2637,7 @@
         <v>73</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>74</v>
@@ -2517,10 +2654,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -2543,13 +2680,13 @@
         <v>73</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -2600,7 +2737,7 @@
         <v>73</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>74</v>
@@ -2617,10 +2754,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -2643,13 +2780,13 @@
         <v>73</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -2700,7 +2837,7 @@
         <v>73</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>74</v>
@@ -2717,10 +2854,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -2728,10 +2865,10 @@
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>73</v>
@@ -2743,13 +2880,13 @@
         <v>73</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>131</v>
+        <v>142</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -2800,13 +2937,13 @@
         <v>73</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="AG20" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>73</v>
@@ -2817,10 +2954,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -2828,7 +2965,7 @@
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="G21" t="s" s="2">
         <v>79</v>
@@ -2843,13 +2980,13 @@
         <v>73</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>127</v>
+        <v>145</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -2900,10 +3037,10 @@
         <v>73</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="AG21" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="AH21" t="s" s="2">
         <v>79</v>
@@ -2917,10 +3054,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -2943,13 +3080,13 @@
         <v>73</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -3000,7 +3137,7 @@
         <v>73</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>74</v>
@@ -3012,6 +3149,1706 @@
         <v>73</v>
       </c>
       <c r="AJ22" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="B23" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="C23" s="2"/>
+      <c r="D23" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E23" s="2"/>
+      <c r="F23" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G23" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H23" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I23" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J23" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K23" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="L23" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="M23" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="N23" s="2"/>
+      <c r="O23" s="2"/>
+      <c r="P23" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q23" s="2"/>
+      <c r="R23" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S23" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T23" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U23" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V23" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W23" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X23" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y23" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z23" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA23" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB23" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC23" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD23" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE23" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF23" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="AG23" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH23" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI23" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ23" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="B24" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="C24" s="2"/>
+      <c r="D24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E24" s="2"/>
+      <c r="F24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G24" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K24" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="L24" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="M24" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="N24" s="2"/>
+      <c r="O24" s="2"/>
+      <c r="P24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q24" s="2"/>
+      <c r="R24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF24" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="AG24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH24" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ24" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="B25" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="C25" s="2"/>
+      <c r="D25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E25" s="2"/>
+      <c r="F25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G25" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K25" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="L25" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="M25" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="N25" s="2"/>
+      <c r="O25" s="2"/>
+      <c r="P25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q25" s="2"/>
+      <c r="R25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF25" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="AG25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH25" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ25" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="B26" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="C26" s="2"/>
+      <c r="D26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E26" s="2"/>
+      <c r="F26" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G26" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K26" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="L26" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="M26" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="N26" s="2"/>
+      <c r="O26" s="2"/>
+      <c r="P26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q26" s="2"/>
+      <c r="R26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF26" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="AG26" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH26" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ26" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="B27" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="C27" s="2"/>
+      <c r="D27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E27" s="2"/>
+      <c r="F27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G27" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K27" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="L27" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="M27" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="N27" s="2"/>
+      <c r="O27" s="2"/>
+      <c r="P27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q27" s="2"/>
+      <c r="R27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF27" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="AG27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH27" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ27" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="B28" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="C28" s="2"/>
+      <c r="D28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E28" s="2"/>
+      <c r="F28" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G28" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K28" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="L28" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="M28" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="N28" s="2"/>
+      <c r="O28" s="2"/>
+      <c r="P28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q28" s="2"/>
+      <c r="R28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF28" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="AG28" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH28" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ28" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="B29" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="C29" s="2"/>
+      <c r="D29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E29" s="2"/>
+      <c r="F29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G29" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K29" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="L29" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="M29" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="N29" s="2"/>
+      <c r="O29" s="2"/>
+      <c r="P29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q29" s="2"/>
+      <c r="R29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF29" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="AG29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH29" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ29" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="B30" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="C30" s="2"/>
+      <c r="D30" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E30" s="2"/>
+      <c r="F30" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G30" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H30" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I30" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J30" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K30" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="L30" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="M30" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="N30" s="2"/>
+      <c r="O30" s="2"/>
+      <c r="P30" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q30" s="2"/>
+      <c r="R30" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S30" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T30" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U30" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V30" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W30" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X30" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y30" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z30" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA30" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB30" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC30" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD30" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE30" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF30" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="AG30" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH30" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI30" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ30" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="B31" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="C31" s="2"/>
+      <c r="D31" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E31" s="2"/>
+      <c r="F31" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G31" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H31" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I31" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J31" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K31" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="L31" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="M31" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="N31" s="2"/>
+      <c r="O31" s="2"/>
+      <c r="P31" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q31" s="2"/>
+      <c r="R31" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S31" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T31" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U31" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V31" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W31" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X31" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y31" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z31" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA31" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB31" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC31" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD31" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE31" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF31" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="AG31" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH31" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI31" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ31" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="B32" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="C32" s="2"/>
+      <c r="D32" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E32" s="2"/>
+      <c r="F32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G32" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H32" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I32" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J32" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K32" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="L32" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="M32" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="N32" s="2"/>
+      <c r="O32" s="2"/>
+      <c r="P32" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q32" s="2"/>
+      <c r="R32" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S32" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T32" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U32" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V32" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W32" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X32" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y32" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z32" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA32" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB32" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC32" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD32" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE32" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF32" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="AG32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH32" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI32" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ32" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="B33" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="C33" s="2"/>
+      <c r="D33" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E33" s="2"/>
+      <c r="F33" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G33" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H33" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I33" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J33" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K33" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="L33" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="M33" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="N33" s="2"/>
+      <c r="O33" s="2"/>
+      <c r="P33" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q33" s="2"/>
+      <c r="R33" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S33" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T33" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U33" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V33" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W33" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X33" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y33" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z33" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA33" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB33" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC33" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD33" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE33" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF33" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="AG33" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH33" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI33" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ33" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="B34" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="C34" s="2"/>
+      <c r="D34" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E34" s="2"/>
+      <c r="F34" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G34" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H34" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I34" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J34" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K34" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="L34" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="M34" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="N34" s="2"/>
+      <c r="O34" s="2"/>
+      <c r="P34" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q34" s="2"/>
+      <c r="R34" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S34" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T34" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U34" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V34" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W34" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X34" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y34" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z34" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA34" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB34" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC34" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD34" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE34" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF34" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="AG34" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH34" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI34" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ34" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="B35" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="C35" s="2"/>
+      <c r="D35" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E35" s="2"/>
+      <c r="F35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G35" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H35" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I35" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J35" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K35" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="L35" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="M35" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="N35" s="2"/>
+      <c r="O35" s="2"/>
+      <c r="P35" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q35" s="2"/>
+      <c r="R35" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S35" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T35" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U35" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V35" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W35" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X35" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y35" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z35" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA35" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB35" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC35" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD35" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE35" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF35" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="AG35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH35" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI35" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ35" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="B36" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="C36" s="2"/>
+      <c r="D36" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E36" s="2"/>
+      <c r="F36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G36" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H36" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I36" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J36" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K36" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="L36" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="M36" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="N36" s="2"/>
+      <c r="O36" s="2"/>
+      <c r="P36" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q36" s="2"/>
+      <c r="R36" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S36" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T36" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U36" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V36" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W36" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X36" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y36" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z36" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA36" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB36" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC36" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD36" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE36" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF36" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="AG36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH36" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI36" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ36" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="B37" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="C37" s="2"/>
+      <c r="D37" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E37" s="2"/>
+      <c r="F37" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G37" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H37" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I37" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J37" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K37" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="L37" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="M37" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="N37" s="2"/>
+      <c r="O37" s="2"/>
+      <c r="P37" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q37" s="2"/>
+      <c r="R37" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S37" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T37" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U37" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V37" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W37" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X37" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y37" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z37" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA37" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB37" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC37" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD37" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE37" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF37" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="AG37" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH37" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI37" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ37" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="B38" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="C38" s="2"/>
+      <c r="D38" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E38" s="2"/>
+      <c r="F38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G38" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H38" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I38" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J38" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K38" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="L38" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="M38" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="N38" s="2"/>
+      <c r="O38" s="2"/>
+      <c r="P38" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q38" s="2"/>
+      <c r="R38" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S38" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T38" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U38" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V38" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W38" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X38" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y38" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z38" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA38" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB38" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC38" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD38" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE38" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF38" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="AG38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH38" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI38" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ38" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="B39" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="C39" s="2"/>
+      <c r="D39" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E39" s="2"/>
+      <c r="F39" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G39" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H39" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I39" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J39" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K39" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="L39" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="M39" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="N39" s="2"/>
+      <c r="O39" s="2"/>
+      <c r="P39" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q39" s="2"/>
+      <c r="R39" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S39" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T39" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U39" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V39" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W39" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X39" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y39" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z39" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA39" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB39" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC39" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD39" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE39" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF39" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="AG39" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH39" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI39" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ39" t="s" s="2">
         <v>73</v>
       </c>
     </row>

--- a/main/ig/StructureDefinition-fr-lm-encounter.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-encounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T14:27:29+00:00</t>
+    <t>2026-06-18T14:40:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-encounter.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-encounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T14:40:49+00:00</t>
+    <t>2026-06-22T09:35:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
